--- a/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet2.xlsx
+++ b/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet2.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77804592-19F0-419A-A05A-857F2D435518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C6A86F-7BE3-48BE-9016-5ACBB3DC65DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
     <sheet name="AppName" sheetId="5" r:id="rId2"/>
     <sheet name="ModuleName" sheetId="6" r:id="rId3"/>
-    <sheet name="ExpenseRequest" sheetId="1" r:id="rId4"/>
+    <sheet name="EventExp" sheetId="1" r:id="rId4"/>
     <sheet name="FirstLevelApprover" sheetId="3" r:id="rId5"/>
     <sheet name="Approver" sheetId="4" r:id="rId6"/>
   </sheets>
@@ -98,9 +98,6 @@
     <t>Users</t>
   </si>
   <si>
-    <t>Sonika Goyal</t>
-  </si>
-  <si>
     <t>1-10</t>
   </si>
   <si>
@@ -183,6 +180,9 @@
   </si>
   <si>
     <t>Expense Request(LWC)</t>
+  </si>
+  <si>
+    <t>Vijay Kumar</t>
   </si>
 </sst>
 </file>
@@ -522,43 +522,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>9</v>
@@ -572,16 +572,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CBB966B-FBE5-4B9C-8027-802A8BDF1019}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -592,16 +592,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9C1758-0B78-4753-AE94-23473BB6C93E}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -612,25 +612,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -681,39 +681,39 @@
       </c>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s">
         <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
       </c>
       <c r="G2" t="s">
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>16</v>
@@ -722,110 +722,110 @@
         <v>17</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="Q2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" t="s">
         <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="Q3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="I4" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>16</v>
@@ -834,10 +834,10 @@
         <v>17</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>18</v>
@@ -849,51 +849,51 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="I5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>18</v>
@@ -914,59 +914,59 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="C4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -991,59 +991,59 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>32</v>
-      </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5">
         <v>9</v>

--- a/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet2.xlsx
+++ b/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C6A86F-7BE3-48BE-9016-5ACBB3DC65DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638D3C37-3622-4335-A9DF-4A2400C50262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,9 +164,6 @@
     <t>klulla@hl.com.test</t>
   </si>
   <si>
-    <t>Bingo@12345</t>
-  </si>
-  <si>
     <t>Dimitri Drone</t>
   </si>
   <si>
@@ -183,6 +180,9 @@
   </si>
   <si>
     <t>Vijay Kumar</t>
+  </si>
+  <si>
+    <t>Bingo@123456</t>
   </si>
 </sst>
 </file>
@@ -522,33 +522,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -556,7 +556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -572,16 +572,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CBB966B-FBE5-4B9C-8027-802A8BDF1019}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -592,16 +592,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9C1758-0B78-4753-AE94-23473BB6C93E}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -612,25 +612,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -681,7 +681,7 @@
       </c>
       <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -689,7 +689,7 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -725,7 +725,7 @@
         <v>26</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>18</v>
@@ -737,7 +737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -745,7 +745,7 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -781,7 +781,7 @@
         <v>26</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>18</v>
@@ -793,7 +793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -837,7 +837,7 @@
         <v>26</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>18</v>
@@ -849,7 +849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -893,7 +893,7 @@
         <v>26</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>18</v>
@@ -914,13 +914,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -928,45 +928,45 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -979,9 +979,9 @@
     <hyperlink ref="A3" r:id="rId3" xr:uid="{9611F415-59B6-42E8-B992-4BDF4D2EA082}"/>
     <hyperlink ref="A4" r:id="rId4" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{37F6AA7D-E662-440D-B4E4-A870523B1294}"/>
     <hyperlink ref="A5" r:id="rId5" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{E27BE1ED-8298-4193-B17A-83CF275488FA}"/>
-    <hyperlink ref="B3" r:id="rId6" xr:uid="{14605699-4141-4582-914A-A11AABC30370}"/>
-    <hyperlink ref="B4" r:id="rId7" xr:uid="{2A32E0A2-8519-48D0-8E95-97389F0BDDD3}"/>
-    <hyperlink ref="B5" r:id="rId8" xr:uid="{F51EEEFC-EDF4-40C8-B70C-EDDA46504948}"/>
+    <hyperlink ref="B3" r:id="rId6" xr:uid="{886FC91F-CAAF-45F2-A975-5F870AEF518C}"/>
+    <hyperlink ref="B4" r:id="rId7" xr:uid="{A10E85CD-7FC6-4B04-AC1C-6CDD77BCF263}"/>
+    <hyperlink ref="B5" r:id="rId8" xr:uid="{A925CB93-F333-403D-878C-A741C0F46057}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -991,13 +991,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -1005,45 +1005,45 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -1054,9 +1054,9 @@
     <hyperlink ref="A3" r:id="rId1" xr:uid="{43CB4C96-EF8E-466C-A098-71C8B71DE9CE}"/>
     <hyperlink ref="A5" r:id="rId2" xr:uid="{F09A18C6-7321-4E0E-B9D9-D9B996CDFDA6}"/>
     <hyperlink ref="B2" r:id="rId3" xr:uid="{98E92ADE-69BD-431C-844E-19278F764E87}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{EB72EFF0-83A0-443B-9185-430E2226C809}"/>
-    <hyperlink ref="B4" r:id="rId5" xr:uid="{D1EB8FFB-0865-4CE2-BE87-112443020732}"/>
-    <hyperlink ref="B5" r:id="rId6" xr:uid="{15A92461-D135-45E8-9987-E8BE39328FE5}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{803DCE0F-4EE6-495C-9229-B36C6651F616}"/>
+    <hyperlink ref="B4" r:id="rId5" xr:uid="{7F7551CD-698C-4FCF-BB99-19198EA00C52}"/>
+    <hyperlink ref="B5" r:id="rId6" xr:uid="{8FF902A9-1DA1-4E99-816B-91BBE7006B96}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId7"/>

--- a/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet2.xlsx
+++ b/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786C30CE-8791-4066-8C5D-DEE18D114B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEAC2E4-B1E7-4EEF-A430-CB213E06CFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -179,10 +179,10 @@
     <t>Vijay Kumar</t>
   </si>
   <si>
-    <t>Bingo@1234567</t>
-  </si>
-  <si>
     <t>FVATestOpportunity Admin</t>
+  </si>
+  <si>
+    <t>Bingo@123456</t>
   </si>
 </sst>
 </file>
@@ -722,7 +722,7 @@
         <v>17</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>48</v>
@@ -778,7 +778,7 @@
         <v>17</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>48</v>
@@ -834,7 +834,7 @@
         <v>17</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>48</v>
@@ -890,7 +890,7 @@
         <v>17</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>48</v>
@@ -933,7 +933,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -944,7 +944,7 @@
         <v>39</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -955,7 +955,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -966,7 +966,7 @@
         <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -979,9 +979,9 @@
     <hyperlink ref="A3" r:id="rId3" xr:uid="{9611F415-59B6-42E8-B992-4BDF4D2EA082}"/>
     <hyperlink ref="A4" r:id="rId4" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{37F6AA7D-E662-440D-B4E4-A870523B1294}"/>
     <hyperlink ref="A5" r:id="rId5" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{E27BE1ED-8298-4193-B17A-83CF275488FA}"/>
-    <hyperlink ref="B3" r:id="rId6" xr:uid="{2961AF1D-45CC-4354-ABBC-9ED635AFD7A5}"/>
-    <hyperlink ref="B4" r:id="rId7" xr:uid="{8B128E76-56CA-45AC-9D74-EEDA70F11F9C}"/>
-    <hyperlink ref="B5" r:id="rId8" xr:uid="{E617EEB0-C5C7-4702-8D28-DE243C9F3BEB}"/>
+    <hyperlink ref="B3" r:id="rId6" xr:uid="{0CAC6E66-EBC4-4507-B28B-E0BDE7F068EF}"/>
+    <hyperlink ref="B4" r:id="rId7" xr:uid="{13F656A2-DDA6-4DDB-AF76-7A12D8BF2472}"/>
+    <hyperlink ref="B5" r:id="rId8" xr:uid="{DDC84C51-2D88-4FBD-BFF5-688F2883D5BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1010,7 +1010,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -1021,7 +1021,7 @@
         <v>36</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>7</v>
@@ -1032,7 +1032,7 @@
         <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -1043,7 +1043,7 @@
         <v>36</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -1054,9 +1054,9 @@
     <hyperlink ref="A3" r:id="rId1" xr:uid="{43CB4C96-EF8E-466C-A098-71C8B71DE9CE}"/>
     <hyperlink ref="A5" r:id="rId2" xr:uid="{F09A18C6-7321-4E0E-B9D9-D9B996CDFDA6}"/>
     <hyperlink ref="B2" r:id="rId3" xr:uid="{98E92ADE-69BD-431C-844E-19278F764E87}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{F457BBE0-EB1F-40A6-AC57-B14495C32F5A}"/>
-    <hyperlink ref="B4" r:id="rId5" xr:uid="{3C00A7D2-F7C5-42C5-9BD2-67CF45BBA308}"/>
-    <hyperlink ref="B5" r:id="rId6" xr:uid="{D893734E-2417-4627-9147-A67EBBB12DF3}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{E91A30B0-7BDA-4F9F-A28F-B48A62AD6D12}"/>
+    <hyperlink ref="B4" r:id="rId5" xr:uid="{D4472A04-A1B2-446C-B484-E82DE3FCBA08}"/>
+    <hyperlink ref="B5" r:id="rId6" xr:uid="{FC02FE68-FA77-4A3A-B5DC-5576EA56B9FC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId7"/>

--- a/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet2.xlsx
+++ b/TestData/LV_T2279_TMTI0036293_ApproveEventExpenseFormAsSecondLevelApproverSet2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEAC2E4-B1E7-4EEF-A430-CB213E06CFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF05CA1-9DC8-43F1-B208-58BF0A58EB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -182,7 +182,7 @@
     <t>FVATestOpportunity Admin</t>
   </si>
   <si>
-    <t>Bingo@123456</t>
+    <t>Bingo@12345</t>
   </si>
 </sst>
 </file>
@@ -979,9 +979,9 @@
     <hyperlink ref="A3" r:id="rId3" xr:uid="{9611F415-59B6-42E8-B992-4BDF4D2EA082}"/>
     <hyperlink ref="A4" r:id="rId4" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{37F6AA7D-E662-440D-B4E4-A870523B1294}"/>
     <hyperlink ref="A5" r:id="rId5" tooltip="mailto:klulla@hl.com.test" display="mailto:klulla@hl.com.test" xr:uid="{E27BE1ED-8298-4193-B17A-83CF275488FA}"/>
-    <hyperlink ref="B3" r:id="rId6" xr:uid="{0CAC6E66-EBC4-4507-B28B-E0BDE7F068EF}"/>
-    <hyperlink ref="B4" r:id="rId7" xr:uid="{13F656A2-DDA6-4DDB-AF76-7A12D8BF2472}"/>
-    <hyperlink ref="B5" r:id="rId8" xr:uid="{DDC84C51-2D88-4FBD-BFF5-688F2883D5BA}"/>
+    <hyperlink ref="B3" r:id="rId6" xr:uid="{ECB58323-0D40-4F6C-B781-320EB2DF6C14}"/>
+    <hyperlink ref="B4" r:id="rId7" xr:uid="{E281D89F-C695-4859-A2A5-EF0363983236}"/>
+    <hyperlink ref="B5" r:id="rId8" xr:uid="{13CC86D8-B484-497B-903C-1E08ACDD73E9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId9"/>
@@ -1054,9 +1054,9 @@
     <hyperlink ref="A3" r:id="rId1" xr:uid="{43CB4C96-EF8E-466C-A098-71C8B71DE9CE}"/>
     <hyperlink ref="A5" r:id="rId2" xr:uid="{F09A18C6-7321-4E0E-B9D9-D9B996CDFDA6}"/>
     <hyperlink ref="B2" r:id="rId3" xr:uid="{98E92ADE-69BD-431C-844E-19278F764E87}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{E91A30B0-7BDA-4F9F-A28F-B48A62AD6D12}"/>
-    <hyperlink ref="B4" r:id="rId5" xr:uid="{D4472A04-A1B2-446C-B484-E82DE3FCBA08}"/>
-    <hyperlink ref="B5" r:id="rId6" xr:uid="{FC02FE68-FA77-4A3A-B5DC-5576EA56B9FC}"/>
+    <hyperlink ref="B3" r:id="rId4" xr:uid="{3448DA0F-E398-4DF8-A666-2ABB6CC42FFA}"/>
+    <hyperlink ref="B4" r:id="rId5" xr:uid="{735B8645-492D-4A0C-BD49-E214809C7C47}"/>
+    <hyperlink ref="B5" r:id="rId6" xr:uid="{5D00EDA9-2BAB-40F9-8800-EA2889BBC935}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId7"/>
